--- a/AAII_Financials/Quarterly/CYATY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CYATY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>CYATY</t>
   </si>
@@ -656,70 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45291</v>
       </c>
       <c r="M7" s="2">
         <v>45291</v>
       </c>
       <c r="N7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -756,8 +759,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -794,8 +800,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -832,8 +841,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -886,8 +899,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -924,8 +940,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -962,8 +981,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1000,8 +1022,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1013,8 +1038,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1051,8 +1077,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1089,8 +1118,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1105,8 +1137,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1143,8 +1176,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1181,8 +1217,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1219,8 +1258,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1257,8 +1299,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1295,8 +1340,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1333,8 +1381,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1371,8 +1422,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1409,8 +1463,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1447,8 +1504,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1485,8 +1545,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1523,8 +1586,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1561,8 +1627,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1599,8 +1668,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1637,8 +1709,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1675,8 +1750,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1713,51 +1791,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45291</v>
       </c>
       <c r="M38" s="2">
         <v>45291</v>
       </c>
       <c r="N38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1772,8 +1856,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1788,75 +1873,79 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54771700</v>
+      </c>
+      <c r="E41" s="3">
         <v>51033300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47682900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>45544700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H41" s="3">
+        <v>45197400</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>41582100</v>
       </c>
-      <c r="I41" s="3">
-        <v>37732700</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>35090900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39965700</v>
-      </c>
-      <c r="L41" s="3">
-        <v>37274000</v>
       </c>
       <c r="M41" s="3">
         <v>37274000</v>
       </c>
       <c r="N41" s="3">
+        <v>37274000</v>
+      </c>
+      <c r="O41" s="3">
         <v>32036900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10033900</v>
+      </c>
+      <c r="E42" s="3">
         <v>8750000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8434400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6076600</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>6157800</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1956700</v>
       </c>
-      <c r="I42" s="3">
-        <v>3136700</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2380800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23100</v>
-      </c>
-      <c r="L42" s="3">
-        <v>1100</v>
       </c>
       <c r="M42" s="3">
         <v>1100</v>
@@ -1864,274 +1953,298 @@
       <c r="N42" s="3">
         <v>1100</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21233800</v>
+      </c>
+      <c r="E43" s="3">
         <v>19815700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>17679000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14375500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3">
+        <v>14077700</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>16475500</v>
       </c>
-      <c r="I43" s="3">
-        <v>15882300</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14711400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15514000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>17598700</v>
       </c>
       <c r="M43" s="3">
         <v>17598700</v>
       </c>
       <c r="N43" s="3">
+        <v>17598700</v>
+      </c>
+      <c r="O43" s="3">
         <v>15431300</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19258500</v>
+      </c>
+      <c r="E44" s="3">
         <v>15794500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13514600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11266900</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3">
+        <v>10088500</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>8197700</v>
       </c>
-      <c r="I44" s="3">
-        <v>7871600</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6612300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6090900</v>
-      </c>
-      <c r="L44" s="3">
-        <v>6407400</v>
       </c>
       <c r="M44" s="3">
         <v>6407400</v>
       </c>
       <c r="N44" s="3">
+        <v>6407400</v>
+      </c>
+      <c r="O44" s="3">
         <v>6699600</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6420300</v>
+      </c>
+      <c r="E45" s="3">
         <v>5006300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3973900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3395400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3">
+        <v>3724200</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>1679100</v>
       </c>
-      <c r="I45" s="3">
-        <v>1919600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2044500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2107800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2150500</v>
       </c>
       <c r="M45" s="3">
         <v>2150500</v>
       </c>
       <c r="N45" s="3">
+        <v>2150500</v>
+      </c>
+      <c r="O45" s="3">
         <v>2211900</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>111718200</v>
+      </c>
+      <c r="E46" s="3">
         <v>100399900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91284700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>80659100</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H46" s="3">
+        <v>79245700</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>69891100</v>
       </c>
-      <c r="I46" s="3">
-        <v>66542800</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60839800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63701400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>63431700</v>
       </c>
       <c r="M46" s="3">
         <v>63431700</v>
       </c>
       <c r="N46" s="3">
+        <v>63431700</v>
+      </c>
+      <c r="O46" s="3">
         <v>56380600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13734900</v>
+      </c>
+      <c r="E47" s="3">
         <v>12723900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12018700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11284700</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H47" s="3">
+        <v>10086100</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>9566700</v>
       </c>
-      <c r="I47" s="3">
-        <v>10005100</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9301800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9231100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>9444800</v>
       </c>
       <c r="M47" s="3">
         <v>9444800</v>
       </c>
       <c r="N47" s="3">
+        <v>9444800</v>
+      </c>
+      <c r="O47" s="3">
         <v>8645400</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30371500</v>
+      </c>
+      <c r="E48" s="3">
         <v>27271900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>25649500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23600700</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H48" s="3">
+        <v>23522700</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>19623500</v>
       </c>
-      <c r="I48" s="3">
-        <v>19495500</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19430300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19547200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>19853300</v>
       </c>
       <c r="M48" s="3">
         <v>19853300</v>
       </c>
       <c r="N48" s="3">
+        <v>19853300</v>
+      </c>
+      <c r="O48" s="3">
         <v>18590800</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2385700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2313000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2302000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2235700</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
+        <v>865100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>2098100</v>
       </c>
-      <c r="I49" s="3">
-        <v>2185700</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2285600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2280900</v>
-      </c>
-      <c r="L49" s="3">
-        <v>2310500</v>
       </c>
       <c r="M49" s="3">
         <v>2310500</v>
       </c>
       <c r="N49" s="3">
+        <v>2310500</v>
+      </c>
+      <c r="O49" s="3">
         <v>2367200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2168,8 +2281,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2206,46 +2322,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4202200</v>
+      </c>
+      <c r="E52" s="3">
         <v>3898900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3325700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3362400</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H52" s="3">
+        <v>3566800</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>2640800</v>
       </c>
-      <c r="I52" s="3">
-        <v>3197400</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2985300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3113700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>2982000</v>
       </c>
       <c r="M52" s="3">
         <v>2982000</v>
       </c>
       <c r="N52" s="3">
+        <v>2982000</v>
+      </c>
+      <c r="O52" s="3">
         <v>3474900</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2282,46 +2404,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>167660000</v>
+      </c>
+      <c r="E54" s="3">
         <v>151699100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>139372600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125868400</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H54" s="3">
+        <v>121050500</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>107774700</v>
       </c>
-      <c r="I54" s="3">
-        <v>105244100</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>98426000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>101279200</v>
-      </c>
-      <c r="L54" s="3">
-        <v>101139200</v>
       </c>
       <c r="M54" s="3">
         <v>101139200</v>
       </c>
       <c r="N54" s="3">
+        <v>101139200</v>
+      </c>
+      <c r="O54" s="3">
         <v>92074700</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2336,8 +2464,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2352,236 +2481,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52332900</v>
+      </c>
+      <c r="E57" s="3">
         <v>43559300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37688100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30189600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H57" s="3">
+        <v>26088200</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
         <v>27172400</v>
       </c>
-      <c r="I57" s="3">
-        <v>26629300</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>25187100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25640700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>27437100</v>
       </c>
       <c r="M57" s="3">
         <v>27437100</v>
       </c>
       <c r="N57" s="3">
+        <v>27437100</v>
+      </c>
+      <c r="O57" s="3">
         <v>26040400</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6311000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5267600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5020800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5663500</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>6284800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>5825700</v>
       </c>
-      <c r="I58" s="3">
-        <v>4465200</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3460400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3434400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3121300</v>
       </c>
       <c r="M58" s="3">
         <v>3121300</v>
       </c>
       <c r="N58" s="3">
+        <v>3121300</v>
+      </c>
+      <c r="O58" s="3">
         <v>2190900</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8738100</v>
+      </c>
+      <c r="E59" s="3">
         <v>10547400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10102100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8971900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H59" s="3">
+        <v>14530200</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>7087300</v>
       </c>
-      <c r="I59" s="3">
-        <v>6499300</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5900100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7256400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>7134400</v>
       </c>
       <c r="M59" s="3">
         <v>7134400</v>
       </c>
       <c r="N59" s="3">
+        <v>7134400</v>
+      </c>
+      <c r="O59" s="3">
         <v>7686600</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71635700</v>
+      </c>
+      <c r="E60" s="3">
         <v>62923700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>57135100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47890300</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H60" s="3">
+        <v>46903200</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
         <v>43453500</v>
       </c>
-      <c r="I60" s="3">
-        <v>40070000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37269200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38634800</v>
-      </c>
-      <c r="L60" s="3">
-        <v>40474600</v>
       </c>
       <c r="M60" s="3">
         <v>40474600</v>
       </c>
       <c r="N60" s="3">
+        <v>40474600</v>
+      </c>
+      <c r="O60" s="3">
         <v>37853000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15624300</v>
+      </c>
+      <c r="E61" s="3">
         <v>13070300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12078700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12437100</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>13499800</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>12854200</v>
       </c>
-      <c r="I61" s="3">
-        <v>14009000</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14983400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14959400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>14521300</v>
       </c>
       <c r="M61" s="3">
         <v>14521300</v>
       </c>
       <c r="N61" s="3">
+        <v>14521300</v>
+      </c>
+      <c r="O61" s="3">
         <v>14480900</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14756700</v>
+      </c>
+      <c r="E62" s="3">
         <v>13897600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12433400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12271500</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H62" s="3">
+        <v>14511900</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
         <v>10074300</v>
       </c>
-      <c r="I62" s="3">
-        <v>10338200</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12052600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8166600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>11057400</v>
       </c>
       <c r="M62" s="3">
         <v>11057400</v>
       </c>
       <c r="N62" s="3">
+        <v>11057400</v>
+      </c>
+      <c r="O62" s="3">
         <v>4571200</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2618,8 +2766,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,8 +2807,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2694,46 +2848,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>106719700</v>
+      </c>
+      <c r="E66" s="3">
         <v>94542400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86326400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77125200</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H66" s="3">
+        <v>75768700</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>70310300</v>
       </c>
-      <c r="I66" s="3">
-        <v>67707500</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68173800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69360600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>70130000</v>
       </c>
       <c r="M66" s="3">
         <v>70130000</v>
       </c>
       <c r="N66" s="3">
+        <v>70130000</v>
+      </c>
+      <c r="O66" s="3">
         <v>64382800</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2748,8 +2908,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2786,8 +2947,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2824,8 +2988,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2862,8 +3029,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2900,46 +3070,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27867000</v>
+      </c>
+      <c r="E72" s="3">
         <v>28655200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25292200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21629900</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H72" s="3">
+        <v>19726400</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>17645500</v>
       </c>
-      <c r="I72" s="3">
-        <v>17018100</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14617600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16060900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>14869400</v>
       </c>
       <c r="M72" s="3">
         <v>14869400</v>
       </c>
       <c r="N72" s="3">
+        <v>14869400</v>
+      </c>
+      <c r="O72" s="3">
         <v>12660600</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2976,8 +3152,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3014,8 +3193,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3052,46 +3234,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>55846400</v>
+      </c>
+      <c r="E76" s="3">
         <v>51796700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48196800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44140900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>41168500</v>
+      </c>
+      <c r="I76" s="3">
         <v>34028800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>33830200</v>
       </c>
-      <c r="I76" s="3">
-        <v>33780900</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27003400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28769500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>27881900</v>
       </c>
       <c r="M76" s="3">
         <v>27881900</v>
       </c>
       <c r="N76" s="3">
+        <v>27881900</v>
+      </c>
+      <c r="O76" s="3">
         <v>24684700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3128,51 +3316,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45291</v>
       </c>
       <c r="M80" s="2">
         <v>45291</v>
       </c>
       <c r="N80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3209,8 +3403,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3225,46 +3422,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1599900</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>3106800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-1742500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1666600</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>2992000</v>
       </c>
-      <c r="I83" s="3">
-        <v>-1325400</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1313800</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
-        <v>1757500</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>1757500</v>
       </c>
       <c r="N83" s="3">
+        <v>1757500</v>
+      </c>
+      <c r="O83" s="3">
         <v>-718900</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3301,8 +3502,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3339,8 +3543,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3377,8 +3584,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3415,8 +3625,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3453,46 +3666,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3906500</v>
+      </c>
+      <c r="E89" s="3">
         <v>4883100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7514500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3086500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>3604100</v>
+      </c>
+      <c r="I89" s="3">
         <v>4529500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4048000</v>
       </c>
-      <c r="I89" s="3">
-        <v>3241100</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2250100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3927400</v>
-      </c>
-      <c r="L89" s="3">
-        <v>5665400</v>
       </c>
       <c r="M89" s="3">
         <v>5665400</v>
       </c>
       <c r="N89" s="3">
+        <v>5665400</v>
+      </c>
+      <c r="O89" s="3">
         <v>2135700</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3507,46 +3726,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1863200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1752400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1387100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-1377800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1425300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1357900</v>
       </c>
-      <c r="I91" s="3">
-        <v>-1060400</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-928700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-980800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-945900</v>
       </c>
       <c r="M91" s="3">
         <v>-945900</v>
       </c>
       <c r="N91" s="3">
+        <v>-945900</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1160100</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3583,8 +3806,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3621,46 +3847,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3283700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2120200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5316300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4357500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-1186400</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2448900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-134400</v>
       </c>
-      <c r="I94" s="3">
-        <v>-1855600</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3711400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1095200</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1304600</v>
       </c>
       <c r="M94" s="3">
         <v>-1304600</v>
       </c>
       <c r="N94" s="3">
+        <v>-1304600</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1071700</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3675,46 +3907,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4715500</v>
+      </c>
+      <c r="E96" s="3">
         <v>90000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>111000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>924700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
+        <v>2876600</v>
+      </c>
+      <c r="I96" s="3">
         <v>827700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>130000</v>
       </c>
-      <c r="I96" s="3">
-        <v>330400</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2921800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>112600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>87500</v>
       </c>
       <c r="M96" s="3">
         <v>87500</v>
       </c>
       <c r="N96" s="3">
+        <v>87500</v>
+      </c>
+      <c r="O96" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3751,8 +3987,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3789,8 +4028,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3827,118 +4069,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2288900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1270400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1513500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2293900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>2778700</v>
+      </c>
+      <c r="I100" s="3">
         <v>96700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>818100</v>
       </c>
-      <c r="I100" s="3">
-        <v>-188200</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3396200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>762300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-18900</v>
       </c>
       <c r="M100" s="3">
         <v>-18900</v>
       </c>
       <c r="N100" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="O100" s="3">
         <v>1187500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F101" s="3">
         <v>91600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-72800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-102200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-140100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>35600</v>
       </c>
-      <c r="I101" s="3">
-        <v>-220200</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>541700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-57300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-18200</v>
       </c>
       <c r="M101" s="3">
         <v>-18200</v>
       </c>
       <c r="N101" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="O101" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2389600</v>
+      </c>
+      <c r="E102" s="3">
         <v>3541100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>392600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3736600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>5232500</v>
+      </c>
+      <c r="I102" s="3">
         <v>2224400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4823300</v>
       </c>
-      <c r="I102" s="3">
-        <v>1124500</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4959800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3454400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>4377500</v>
       </c>
       <c r="M102" s="3">
         <v>4377500</v>
       </c>
       <c r="N102" s="3">
+        <v>4377500</v>
+      </c>
+      <c r="O102" s="3">
         <v>2031300</v>
       </c>
     </row>
